--- a/tiflow/develop/2.0.0-ballot.1/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/ConceptMap/TIFLOW-CM-TelemetryDataStatusCodes</t>
+    <t>https://gematik.de/fhir/tiflow/ConceptMap/TIFLOW-CM-TelemetryDataStatusCodes</t>
   </si>
   <si>
     <t>Version</t>

--- a/tiflow/develop/2.0.0-ballot.1/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="189">
   <si>
     <t>Property</t>
   </si>
@@ -358,6 +358,12 @@
   </si>
   <si>
     <t>79238</t>
+  </si>
+  <si>
+    <t>TIFLOW_POPP_TOKEN_INVALID</t>
+  </si>
+  <si>
+    <t>79273</t>
   </si>
   <si>
     <t>https://gematik.de/fhir/erp/CodeSystem/tiflow-chargeitem-operation-outcome-details-cs</t>
@@ -833,7 +839,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1389,6 +1395,19 @@
         <v>112</v>
       </c>
       <c r="E42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E43" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1419,7 +1438,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1436,66 +1455,66 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1528,7 +1547,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1545,40 +1564,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1611,7 +1630,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1628,105 +1647,105 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -1759,7 +1778,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1776,40 +1795,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1842,7 +1861,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1859,53 +1878,53 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1938,7 +1957,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1955,144 +1974,144 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E13" s="2"/>
     </row>

--- a/tiflow/develop/2.0.0-ballot.1/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="193">
   <si>
     <t>Property</t>
   </si>
@@ -364,6 +364,18 @@
   </si>
   <si>
     <t>79273</t>
+  </si>
+  <si>
+    <t>TIFLOW_INTERNAL_ERROR</t>
+  </si>
+  <si>
+    <t>79274</t>
+  </si>
+  <si>
+    <t>TIFLOW_TIMEOUT</t>
+  </si>
+  <si>
+    <t>79275</t>
   </si>
   <si>
     <t>https://gematik.de/fhir/erp/CodeSystem/tiflow-chargeitem-operation-outcome-details-cs</t>
@@ -839,7 +851,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1408,6 +1420,32 @@
         <v>114</v>
       </c>
       <c r="E43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E45" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1438,7 +1476,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1455,66 +1493,66 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1547,7 +1585,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1564,40 +1602,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1630,7 +1668,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1647,105 +1685,105 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -1778,7 +1816,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1795,40 +1833,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1861,7 +1899,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1878,53 +1916,53 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1957,7 +1995,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -1974,144 +2012,144 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E13" s="2"/>
     </row>
